--- a/Tratamento/src/Dados_Limpos/novos/limpo_cobasi_20251103_201508.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_cobasi_20251103_201508.xlsx
@@ -5452,7 +5452,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5522,7 +5522,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5732,7 +5732,7 @@
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5872,7 +5872,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_cobasi_20251103_201508.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_cobasi_20251103_201508.xlsx
@@ -5452,7 +5452,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5522,7 +5522,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5732,7 +5732,7 @@
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5872,7 +5872,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
